--- a/technical-triz/innovation-checklist/assets/TRU_ISQ_EN.xlsx
+++ b/technical-triz/innovation-checklist/assets/TRU_ISQ_EN.xlsx
@@ -1,141 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28227"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jens\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F92DAAD-08A3-4D45-8CB8-571BC4161558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="340" yWindow="1220" windowWidth="16660" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="340" yWindow="1220" windowWidth="16660" windowHeight="17880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ISQ EN" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ISQ EN" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Question</t>
-  </si>
-  <si>
-    <t>Subsystems-Supersystems</t>
-  </si>
-  <si>
-    <t>Cause-Effect</t>
-  </si>
-  <si>
-    <t>Past-Future</t>
-  </si>
-  <si>
-    <t>Input-Output</t>
-  </si>
-  <si>
-    <t>Resources-Options</t>
-  </si>
-  <si>
-    <t>Criteria-Solution Spaces</t>
-  </si>
-  <si>
-    <t>What is the primary function of the system?</t>
-  </si>
-  <si>
-    <t>How do the subsystems interact to achieve this function?</t>
-  </si>
-  <si>
-    <t>How does the supersystem interact with this system? In what ways does it affect its functions, and what are the main reasons for these interactions?</t>
-  </si>
-  <si>
-    <t>What are the primary cause-effect relationships of the issue, and how do they propagate throughout the system?</t>
-  </si>
-  <si>
-    <t>What are the known (engineering or physical) contradictions? What conflicts are there?</t>
-  </si>
-  <si>
-    <t>What assumptions exist about these relationships that should be verified?</t>
-  </si>
-  <si>
-    <t>When did the problem first occur, and what changes or events led to its occurrence?</t>
-  </si>
-  <si>
-    <t>What past attempts to solve the problem have been made, and why did they fail?</t>
-  </si>
-  <si>
-    <t>What are the possible future consequences if the problem remains unresolved?</t>
-  </si>
-  <si>
-    <t>What is the desired state or goal for the future?</t>
-  </si>
-  <si>
-    <t>What are the key inputs required for the system to function?</t>
-  </si>
-  <si>
-    <t>What outputs does the system produce?</t>
-  </si>
-  <si>
-    <t>How do the inputs and outputs contribute to or hinder achieving the main function of the system?</t>
-  </si>
-  <si>
-    <t>Are there any undesirable inputs or outputs that contribute to the problem?</t>
-  </si>
-  <si>
-    <t>What resources (materials, energy, time, space, information or functions) are available in or near the system?</t>
-  </si>
-  <si>
-    <t>What restrictions limit the available options?</t>
-  </si>
-  <si>
-    <t>Are there unused, hidden or overlooked resources in the surroundings of the system that could be utilized?</t>
-  </si>
-  <si>
-    <t>What technical, economic or operational criteria must the solution fulfill?</t>
-  </si>
-  <si>
-    <t>What constraints define the acceptable solution space?</t>
-  </si>
-  <si>
-    <t>What solution concepts are disallowed, and why?</t>
-  </si>
-  <si>
-    <t>How is the success of the solution measured?</t>
-  </si>
-  <si>
-    <t>Answer</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -169,17 +69,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -188,40 +88,101 @@
   </cellStyles>
   <dxfs count="5">
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="top"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="top"/>
     </dxf>
     <dxf>
-      <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EF02604C-01C3-4726-908D-5670FBA6CF03}" name="Tabelle1" displayName="Tabelle1" ref="A1:C22" totalsRowShown="0" headerRowDxfId="4" dataDxfId="0">
-  <autoFilter ref="A1:C22" xr:uid="{EF02604C-01C3-4726-908D-5670FBA6CF03}"/>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{169F4B50-1BBE-4FEA-9F6F-16FFFF749AFB}" name="Category" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{D9C33FD0-8CC4-45B0-8304-11779E5BF1EB}" name="Question" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{5C774D3D-D24D-4507-9CBD-FF0F1652ADD5}" name="Answer" dataDxfId="1"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabelle1" displayName="Tabelle1" ref="A1:D22" headerRowCount="1" totalsRowShown="0" headerRowDxfId="4" dataDxfId="0">
+  <autoFilter ref="A1:C22"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="Category" dataDxfId="3"/>
+    <tableColumn id="2" name="Question" dataDxfId="2"/>
+    <tableColumn id="3" name="Answer" dataDxfId="1"/>
+    <tableColumn id="4" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -513,218 +474,340 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="25.6328125" customWidth="1"/>
-    <col min="2" max="3" width="60.6328125" customWidth="1"/>
+    <col width="25.6328125" customWidth="1" min="1" max="1"/>
+    <col width="60.6328125" customWidth="1" min="2" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="4"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="4"/>
-    </row>
-    <row r="4" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="4"/>
-    </row>
-    <row r="5" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="4"/>
-    </row>
-    <row r="6" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="4"/>
-    </row>
-    <row r="7" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="4"/>
-    </row>
-    <row r="8" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="4"/>
-    </row>
-    <row r="9" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="4"/>
-    </row>
-    <row r="10" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="4"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="4"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="4"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="4"/>
-    </row>
-    <row r="14" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="4"/>
-    </row>
-    <row r="15" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="4"/>
-    </row>
-    <row r="16" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A16" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="4"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="4"/>
-    </row>
-    <row r="18" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A18" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="4"/>
-    </row>
-    <row r="19" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A19" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="4"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" s="4"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C21" s="4"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22" s="4"/>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Answer</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Subsystems-Supersystems</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>What is the primary function of the system?</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Subsystems-Supersystems</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>How do the subsystems interact to achieve this function?</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+    </row>
+    <row r="4" ht="43.5" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Subsystems-Supersystems</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>How does the supersystem interact with this system? In what ways does it affect its functions, and what are the main reasons for these interactions?</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+    </row>
+    <row r="5" ht="29" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Cause-Effect</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>What are the primary cause-effect relationships of the issue, and how do they propagate throughout the system?</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+    </row>
+    <row r="6" ht="29" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Cause-Effect</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>What are the known (engineering or physical) contradictions? What conflicts are there?</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+    </row>
+    <row r="7" ht="29" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Cause-Effect</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>What assumptions exist about these relationships that should be verified?</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+    </row>
+    <row r="8" ht="29" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Past-Future</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>When did the problem first occur, and what changes or events led to its occurrence?</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+    </row>
+    <row r="9" ht="29" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Past-Future</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>What past attempts to solve the problem have been made, and why did they fail?</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="n"/>
+    </row>
+    <row r="10" ht="29" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Past-Future</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>What are the possible future consequences if the problem remains unresolved?</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Past-Future</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>What is the desired state or goal for the future?</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Input-Output</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>What are the key inputs required for the system to function?</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Input-Output</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>What outputs does the system produce?</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+    </row>
+    <row r="14" ht="29" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Input-Output</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>How do the inputs and outputs contribute to or hinder achieving the main function of the system?</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+    </row>
+    <row r="15" ht="29" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Input-Output</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Are there any undesirable inputs or outputs that contribute to the problem?</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="n"/>
+    </row>
+    <row r="16" ht="29" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Resources-Options</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>What resources (materials, energy, time, space, information or functions) are available in or near the system?</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Resources-Options</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>What restrictions limit the available options?</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+    </row>
+    <row r="18" ht="29" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Resources-Options</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Are there unused, hidden or overlooked resources in the surroundings of the system that could be utilized?</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+    </row>
+    <row r="19" ht="29" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Criteria-Solution Spaces</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>What technical, economic or operational criteria must the solution fulfill?</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Criteria-Solution Spaces</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>What constraints define the acceptable solution space?</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Criteria-Solution Spaces</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>What solution concepts are disallowed, and why?</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Criteria-Solution Spaces</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>How is the success of the solution measured?</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
--- a/technical-triz/innovation-checklist/assets/TRU_ISQ_EN.xlsx
+++ b/technical-triz/innovation-checklist/assets/TRU_ISQ_EN.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="33">
   <si>
     <t>Category</t>
   </si>
@@ -113,6 +113,12 @@
   </si>
   <si>
     <t>How is the success of the solution measured?</t>
+  </si>
+  <si>
+    <t>System name</t>
+  </si>
+  <si>
+    <t>Date</t>
   </si>
 </sst>
 </file>
@@ -219,8 +225,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabelle1" displayName="Tabelle1" ref="A1:D22" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
-  <autoFilter ref="A1:D22" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabelle1" displayName="Tabelle1" ref="A4:D25" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+  <autoFilter ref="A4:D25" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Category" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Question" dataDxfId="1"/>
@@ -518,7 +524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25.6328125" customWidth="1"/>
@@ -529,227 +535,239 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="3"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="3"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B5" s="4" t="s">
         <v>5</v>
-      </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-    </row>
-    <row r="4" spans="1:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-    </row>
-    <row r="5" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>9</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
     </row>
-    <row r="7" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
     </row>
     <row r="8" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
     </row>
     <row r="9" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
     </row>
     <row r="10" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
     </row>
-    <row r="15" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
     </row>
     <row r="18" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
     </row>
     <row r="19" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>26</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/technical-triz/innovation-checklist/assets/TRU_ISQ_EN.xlsx
+++ b/technical-triz/innovation-checklist/assets/TRU_ISQ_EN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jens\dev\github\truinorva\triz-skills\technical-triz\innovation-checklist\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87B0BB4A-7F75-4949-AD9A-E03DF66B962C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{155FCF05-4D84-4723-BAB7-B8527EAC1718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -125,7 +125,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -141,13 +141,33 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -177,7 +197,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -190,6 +210,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -534,16 +560,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="3"/>
+      <c r="B1" s="5"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="3"/>
+      <c r="B2" s="5"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
